--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-automation-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-automation-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Nếu chạy song song mà dùng chung một WebDriver instance tĩnh (static driver), các luồng chạy test sẽ tranh chấp điều khiển cùng 1 cửa sổ trình duyệt (luồng này click, luồng kia close tab), dẫn đến sập toàn bộ bộ test. ThreadLocal bọc driver instance giúp cô lập hoàn toàn driver trên từng thread chạy độc lập.</v>
       </c>
       <c r="F2" t="str">
+        <v>Để hệ thống tự động sửa đổi mã nguồn code test khi phát sinh lỗi xung đột tài nguyên giữa các luồng — tự sửa lỗi</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Để ép buộc các máy tính chạy test song song phải có cấu hình bộ vi xử lý tối thiểu là 8 nhân 16 luồng — yêu cầu cấu hình CPU</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Để tự động nén kích thước của các file ảnh chụp màn hình lỗi khi lưu xuống ổ cứng của máy chủ CI/CD — nén ảnh lỗi</v>
+      </c>
+      <c r="I2" t="str">
         <v>Để đảm bảo mỗi luồng chạy test (thread) sở hữu một WebDriver instance riêng biệt độc lập, tránh xung đột chia sẻ tài nguyên driver làm crash trình duyệt và gây lẫn lộn trạng thái test giữa các test case — ThreadLocal cô lập WebDriver instance</v>
       </c>
-      <c r="G2" t="str">
-        <v>Để tự động nén kích thước của các file ảnh chụp màn hình lỗi khi lưu xuống ổ cứng của máy chủ CI/CD — nén ảnh lỗi</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Để ép buộc các máy tính chạy test song song phải có cấu hình bộ vi xử lý tối thiểu là 8 nhân 16 luồng — yêu cầu cấu hình CPU</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Để hệ thống tự động sửa đổi mã nguồn code test khi phát sinh lỗi xung đột tài nguyên giữa các luồng — tự sửa lỗi</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Playwright/Cypress chạy trên kiến trúc hiện đại (NodeJS process giao tiếp trực tiếp với browser qua CDP/WebSocket thay vì JSON Wire Protocol qua HTTP server như Selenium). Nó tự động chạy các Actionability Checks (Attached, Visible, Stable, Enabled, Receives Events) trước khi click, giúp triệt tiêu hầu hết lỗi Flaky do bất đồng bộ render.</v>
       </c>
       <c r="F3" t="str">
+        <v>Chỉ hỗ trợ chạy các kịch bản test tự động viết bằng ngôn ngữ C++ giúp chạy nhanh gấp 10 lần — hỗ trợ ngôn ngữ C++</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Tự động bỏ qua các lỗi assertion thất bại để đảm bảo toàn bộ test suite luôn báo cáo kết quả Passed — bỏ qua lỗi test</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Tự động tải lại trang web liên tục cho đến khi hệ thống phản hồi thành công mã status code 200 — tự động reload trang</v>
+      </c>
+      <c r="I3" t="str">
         <v>Tự động kiểm tra trước khi tương tác xem phần tử có hiển thị, có kích thước ổn định, có nhận sự kiện click được không (actionability checks) trước khi thực hiện lệnh, loại bỏ việc viết lệnh chờ đợi thủ công — tự động check điều kiện tương tác Actionability</v>
       </c>
-      <c r="G3" t="str">
-        <v>Tự động tải lại trang web liên tục cho đến khi hệ thống phản hồi thành công mã status code 200 — tự động reload trang</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Chỉ hỗ trợ chạy các kịch bản test tự động viết bằng ngôn ngữ C++ giúp chạy nhanh gấp 10 lần — hỗ trợ ngôn ngữ C++</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Tự động bỏ qua các lỗi assertion thất bại để đảm bảo toàn bộ test suite luôn báo cáo kết quả Passed — bỏ qua lỗi test</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Kỹ thuật tốt nhất (Best Practice) là phối hợp với Dev thêm thuộc tính `data-testid` hoặc `data-qa` vào mã nguồn HTML. Thuộc tính này được giữ nguyên khi build và không thay đổi theo CSS style hay logic JS, giúp định vị phần tử bền bỉ 100% qua các đợt refactor.</v>
       </c>
       <c r="F4" t="str">
-        <v>Sử dụng XPath/CSS theo mối quan hệ gia đình (Sibling, Parent-Child) đi từ một gốc phần tử tĩnh ổn định gần nhất, hoặc yêu cầu dev thêm thuộc tính tùy chỉnh chuyên biệt phục vụ test (như `data-testid="submit-btn"`) — sử dụng data-testid và mối quan hệ quan hệ trục</v>
+        <v>Sử dụng đường dẫn tuyệt đối (Absolute XPath) đi từ thẻ gốc html của trang web — đường dẫn tuyệt đối rủi ro cao</v>
       </c>
       <c r="G4" t="str">
-        <v>Sử dụng đường dẫn tuyệt đối (Absolute XPath) đi từ thẻ gốc html của trang web — đường dẫn tuyệt đối rủi ro cao</v>
+        <v>Copy trực tiếp chuỗi class động (như `class="sc-gqjmNp iKqDqf"`) vào locator của script test — sử dụng class động xáo trộn</v>
       </c>
       <c r="H4" t="str">
         <v>Sử dụng chỉ mục cứng (Index) để tìm kiếm phần tử (ví dụ nút bấm thứ 5 trên trang) — sử dụng index cứng dễ gãy</v>
       </c>
       <c r="I4" t="str">
-        <v>Copy trực tiếp chuỗi class động (như `class="sc-gqjmNp iKqDqf"`) vào locator của script test — sử dụng class động xáo trộn</v>
+        <v>Sử dụng XPath/CSS theo mối quan hệ gia đình (Sibling, Parent-Child) đi từ một gốc phần tử tĩnh ổn định gần nhất, hoặc yêu cầu dev thêm thuộc tính tùy chỉnh chuyên biệt phục vụ test (như `data-testid="submit-btn"`) — sử dụng data-testid và mối quan hệ quan hệ trục</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Quản lý dữ liệu test (Test Data Management) là phần khó nhất trong Automation. Teardown script (thường là gọi API DELETE hoặc gọi trực tiếp SQL script xóa dữ liệu test theo tag/prefix nhận diện) giúp trả môi trường về trạng thái sạch (Clean State) sẵn sàng cho lượt chạy tiếp theo.</v>
       </c>
       <c r="F5" t="str">
+        <v>Yêu cầu nhân viên QA hàng ngày phải mở màn hình admin của hệ thống lên và tự bấm xóa bằng tay từng đơn hàng rác — xóa tay thủ công</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tắt toàn bộ tính năng ghi nhật ký và lưu trữ dữ liệu của máy chủ database của môi trường test — tắt lưu trữ database</v>
+      </c>
+      <c r="H5" t="str">
         <v>Thiết kế các API dọn dẹp (Cleanup APIs/Teardown scripts) chạy ở bước cuối cùng `@AfterSuite` để xóa các dữ liệu rác đã tạo dựa trên ID giao dịch, hoặc kết nối trực tiếp database chạy lệnh SQL DELETE trong mã test — thiết kế Teardown dọn dẹp dữ liệu rác</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Yêu cầu nhân viên QA hàng ngày phải mở màn hình admin của hệ thống lên và tự bấm xóa bằng tay từng đơn hàng rác — xóa tay thủ công</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tắt toàn bộ tính năng ghi nhật ký và lưu trữ dữ liệu của máy chủ database của môi trường test — tắt lưu trữ database</v>
       </c>
       <c r="I5" t="str">
         <v>Chỉ chạy các kịch bản test API dạng GET để đọc dữ liệu chứ không chạy các API dạng POST/PUT để tránh tạo dữ liệu rác — hạn chế loại test</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -655,13 +655,13 @@
         <v>Keyword-Driven định nghĩa các từ khóa đại diện cho thao tác (như click_element, enter_text) trong file Excel; BDD sử dụng ngôn ngữ tự nhiên Gherkin (Given-When-Then) để mô tả kịch bản nghiệp vụ liên kết với Step Definitions code — từ khóa thao tác Excel vs ngôn ngữ tự nhiên Gherkin</v>
       </c>
       <c r="G8" t="str">
+        <v>Keyword-Driven bắt buộc phải trả phí bản quyền thương mại; còn BDD hoàn toàn miễn phí — so sánh chi phí bản quyền</v>
+      </c>
+      <c r="H8" t="str">
         <v>Keyword-Driven chỉ dùng cho kiểm thử thiết bị phần cứng; còn BDD chỉ dùng cho kiểm thử ứng dụng di động — phân loại đối tượng test</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>Keyword-Driven chạy nhanh hơn BDD gấp 100 lần do không phải phân tích cú pháp chuỗi văn bản — so sánh hiệu năng tốc độ</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Keyword-Driven bắt buộc phải trả phí bản quyền thương mại; còn BDD hoàn toàn miễn phí — so sánh chi phí bản quyền</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>Khi test suite chạy tự động 1000 test cases trên CI/CD không có người giám sát, nếu có 10 cases bị fail, QA không thể ngồi đoán lỗi. Sử dụng TestNG `ITestListener` giúp lắng nghe sự kiện fail, lập tức kích hoạt `TakesScreenshot` chụp lại trạng thái UI và đính kèm vào báo cáo (như Allure Report) giúp tiết kiệm hàng giờ debug.</v>
       </c>
       <c r="F9" t="str">
-        <v>Để cung cấp bằng chứng trực quan tức thời tại thời điểm lỗi phục vụ debug nhanh; thiết kế bằng cách viết một Class Listener kế thừa `TestListenerAdapter` và ghi đè phương thức `onTestFailure` để gọi hàm chụp ảnh màn hình — thiết kế Test Listener chụp ảnh khi fail</v>
+        <v>Để khóa quyền truy cập vào mã nguồn của lập trình viên đã làm xảy ra lỗi đó — khóa quyền truy cập của dev</v>
       </c>
       <c r="G9" t="str">
         <v>Để hệ thống tự động gửi ảnh chụp lỗi lên mạng xã hội Facebook của công ty nhằm công khai lỗi — công khai lỗi</v>
       </c>
       <c r="H9" t="str">
-        <v>Để khóa quyền truy cập vào mã nguồn của lập trình viên đã làm xảy ra lỗi đó — khóa quyền truy cập của dev</v>
+        <v>Để driver tự động dừng toàn bộ tiến trình chạy test của các test case tiếp theo trong suite — dừng toàn bộ test suite</v>
       </c>
       <c r="I9" t="str">
-        <v>Để driver tự động dừng toàn bộ tiến trình chạy test của các test case tiếp theo trong suite — dừng toàn bộ test suite</v>
+        <v>Để cung cấp bằng chứng trực quan tức thời tại thời điểm lỗi phục vụ debug nhanh; thiết kế bằng cách viết một Class Listener kế thừa `TestListenerAdapter` và ghi đè phương thức `onTestFailure` để gọi hàm chụp ảnh màn hình — thiết kế Test Listener chụp ảnh khi fail</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>RestAssured tích hợp mạnh mẽ với JsonPath và Hamcrest Matchers. Sử dụng biểu thức JsonPath (như `products.price`) kết hợp Hamcrest matcher `everyItem()` giúp kiểm tra nhanh chóng và viết code ngắn gọn, dễ đọc.</v>
       </c>
       <c r="F10" t="str">
+        <v>Yêu cầu lập trình viên Backend viết riêng một API mới chỉ trả về đúng 1 con số 0 hoặc 1 biểu thị trạng thái giá sản phẩm — tạo API phụ</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Chuyển đổi toàn bộ chuỗi Response Body sang định dạng file XML rồi mới tiến hành kiểm tra — convert sang XML</v>
+      </c>
+      <c r="H10" t="str">
         <v>Sử dụng hàm `.body("products.price", everyItem(greaterThan(0))).body("products.currency", everyItem(equalTo("VND")))` kết hợp thư viện Hamcrest matchers — Hamcrest matchers validate mảng JSON</v>
       </c>
-      <c r="G10" t="str">
+      <c r="I10" t="str">
         <v>Viết các vòng lặp for/while thủ công trong code Java để duyệt qua từng ký tự của chuỗi Response Body dạng text thô — duyệt chuỗi thô thủ công</v>
       </c>
-      <c r="H10" t="str">
-        <v>Chuyển đổi toàn bộ chuỗi Response Body sang định dạng file XML rồi mới tiến hành kiểm tra — convert sang XML</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Yêu cầu lập trình viên Backend viết riêng một API mới chỉ trả về đúng 1 con số 0 hoặc 1 biểu thị trạng thái giá sản phẩm — tạo API phụ</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -748,7 +748,7 @@
         <v>Nếu không dùng DDT, để test form đăng nhập với 10 tài khoản khác nhau, bạn phải viết 10 test cases giống hệt nhau (chỉ khác data), gây trùng lặp code lớn (code duplication). Sử dụng DataProvider giúp viết duy nhất 1 kịch bản test và nạp 10 dòng data chạy lặp lại, khi spec thay đổi chỉ cần sửa 1 chỗ duy nhất.</v>
       </c>
       <c r="F11" t="str">
-        <v>Vì nó tách biệt hoàn toàn mã nguồn kiểm thử (test logic) khỏi dữ liệu đầu vào (test data); khi cần bổ sung kịch bản test biên, chỉ cần bổ sung dữ liệu trong tệp tin cấu hình/DataProvider mà không cần sửa code test — tách biệt logic và dữ liệu dễ bảo trì</v>
+        <v>Vì nó cho phép chạy test tự động mà không cần mở trình duyệt web — chạy không cần trình duyệt</v>
       </c>
       <c r="G11" t="str">
         <v>Vì `@DataProvider` tự động sửa các lỗi logic code của ứng dụng đang được kiểm thử — tự sửa lỗi ứng dụng</v>
@@ -757,10 +757,10 @@
         <v>Vì nó bắt buộc toàn bộ dữ liệu test phải được mã hóa bằng thuật toán bảo mật SHA-256 trước khi chạy — mã hóa dữ liệu test</v>
       </c>
       <c r="I11" t="str">
-        <v>Vì nó cho phép chạy test tự động mà không cần mở trình duyệt web — chạy không cần trình duyệt</v>
+        <v>Vì nó tách biệt hoàn toàn mã nguồn kiểm thử (test logic) khỏi dữ liệu đầu vào (test data); khi cần bổ sung kịch bản test biên, chỉ cần bổ sung dữ liệu trong tệp tin cấu hình/DataProvider mà không cần sửa code test — tách biệt logic và dữ liệu dễ bảo trì</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
